--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -197,13 +197,13 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
   </si>
   <si>
     <t>Mendoza Velazquez Laura Elena</t>
@@ -995,10 +995,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -1049,10 +1049,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -1072,10 +1072,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -1126,10 +1126,10 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1149,10 +1149,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1203,10 +1203,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1226,10 +1226,10 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1280,10 +1280,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1303,10 +1303,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1357,10 +1357,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1380,10 +1380,10 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -1434,10 +1434,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1460,7 +1460,7 @@
         <v>-1</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1514,7 +1514,7 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1534,10 +1534,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1588,10 +1588,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1611,10 +1611,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1665,10 +1665,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1688,10 +1688,10 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1742,10 +1742,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1765,10 +1765,10 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1819,10 +1819,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1842,10 +1842,10 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1896,10 +1896,10 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1919,10 +1919,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -1973,10 +1973,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1996,10 +1996,10 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -2050,10 +2050,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2073,10 +2073,10 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>-1</v>
@@ -2127,10 +2127,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2150,10 +2150,10 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>-1</v>
@@ -2204,10 +2204,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2227,10 +2227,10 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2281,10 +2281,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2304,10 +2304,10 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2358,10 +2358,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2381,10 +2381,10 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>-1</v>
@@ -2435,10 +2435,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2458,10 +2458,10 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2512,10 +2512,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2538,7 +2538,7 @@
         <v>-1</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2592,7 +2592,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2612,10 +2612,10 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2666,10 +2666,10 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2689,10 +2689,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2743,10 +2743,10 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2766,10 +2766,10 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -2820,10 +2820,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2843,10 +2843,10 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -2897,10 +2897,10 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -2920,10 +2920,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -2974,10 +2974,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -2997,10 +2997,10 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -3051,10 +3051,10 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3074,10 +3074,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -3128,10 +3128,10 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3151,10 +3151,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3205,10 +3205,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3228,10 +3228,10 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3282,10 +3282,10 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3305,10 +3305,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>-1</v>
@@ -3359,10 +3359,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3382,10 +3382,10 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -3436,10 +3436,10 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3459,10 +3459,10 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D36">
         <v>-1</v>
@@ -3513,10 +3513,10 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3536,10 +3536,10 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>-1</v>
@@ -3590,10 +3590,10 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>-1</v>
@@ -3613,10 +3613,10 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>-1</v>
@@ -3667,10 +3667,10 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>-1</v>
@@ -3690,10 +3690,10 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>-1</v>
@@ -3744,10 +3744,10 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>-1</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3882,27 +3882,30 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>27</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>75</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>36</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3911,27 +3914,30 @@
         <v>36</v>
       </c>
       <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>86.11</v>
+      </c>
+      <c r="G5">
+        <v>13.89</v>
+      </c>
+      <c r="H5">
+        <v>5.9</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>36</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3940,25 +3946,25 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>94.44</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4000,7 +4006,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4069,56 +4075,56 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920368</v>
+        <v>20330051920156</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920368</v>
+        <v>20330051920156</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920156</v>
+        <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4129,16 +4135,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920156</v>
+        <v>20330051920157</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4149,56 +4155,56 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920156</v>
+        <v>20330051920158</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920156</v>
+        <v>20330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920157</v>
+        <v>20330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4209,16 +4215,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920157</v>
+        <v>20330051920369</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -4229,56 +4235,56 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920157</v>
+        <v>20330051920160</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920157</v>
+        <v>20330051920160</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920158</v>
+        <v>20330051920161</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4289,16 +4295,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920158</v>
+        <v>20330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -4309,616 +4315,616 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920158</v>
+        <v>20330051920161</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920158</v>
+        <v>20330051920162</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920369</v>
+        <v>20330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920369</v>
+        <v>20330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920369</v>
+        <v>20330051920163</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920369</v>
+        <v>20330051920164</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920160</v>
+        <v>20330051920164</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920160</v>
+        <v>20330051920370</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920160</v>
+        <v>20330051920370</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920160</v>
+        <v>20330051920372</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920161</v>
+        <v>20330051920372</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920161</v>
+        <v>20330051920165</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920161</v>
+        <v>20330051920165</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920161</v>
+        <v>20330051920167</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920162</v>
+        <v>20330051920167</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920162</v>
+        <v>20330051920166</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920162</v>
+        <v>20330051920166</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920162</v>
+        <v>20330051920168</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920163</v>
+        <v>20330051920168</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920163</v>
+        <v>20330051920371</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920163</v>
+        <v>20330051920371</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920163</v>
+        <v>20330051920171</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920164</v>
+        <v>20330051920171</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920164</v>
+        <v>20330051920172</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920164</v>
+        <v>20330051920172</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920164</v>
+        <v>20330051920173</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920370</v>
+        <v>20330051920173</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920370</v>
+        <v>20330051920174</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920370</v>
+        <v>20330051920174</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920370</v>
+        <v>20330051920174</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
         <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920372</v>
+        <v>20330051920306</v>
       </c>
       <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
         <v>77</v>
       </c>
-      <c r="C46" t="s">
-        <v>109</v>
-      </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -4929,16 +4935,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920372</v>
+        <v>20330051920306</v>
       </c>
       <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" t="s">
         <v>77</v>
       </c>
-      <c r="C47" t="s">
-        <v>109</v>
-      </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -4949,56 +4955,56 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920372</v>
+        <v>20330051920177</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920372</v>
+        <v>20330051920177</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920165</v>
+        <v>20330051920178</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
@@ -5009,16 +5015,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920165</v>
+        <v>20330051920178</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
@@ -5029,56 +5035,56 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920165</v>
+        <v>20330051920179</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920165</v>
+        <v>20330051920179</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920167</v>
+        <v>20330051920180</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -5089,16 +5095,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920167</v>
+        <v>20330051920180</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -5109,56 +5115,56 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920167</v>
+        <v>20330051920373</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920167</v>
+        <v>20330051920373</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920166</v>
+        <v>20330051920254</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
@@ -5169,16 +5175,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920166</v>
+        <v>20330051920254</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -5189,56 +5195,56 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920166</v>
+        <v>20330051920181</v>
       </c>
       <c r="B60" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920166</v>
+        <v>20330051920181</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920168</v>
+        <v>20330051920393</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
@@ -5249,16 +5255,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920168</v>
+        <v>20330051920393</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
@@ -5269,56 +5275,56 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920168</v>
+        <v>20330051920182</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E64" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920168</v>
+        <v>20330051920182</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D65" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E65" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920371</v>
+        <v>20330051920183</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
         <v>7</v>
@@ -5329,16 +5335,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>20330051920371</v>
+        <v>20330051920183</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -5349,56 +5355,56 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>20330051920371</v>
+        <v>20330051920184</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D68" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>20330051920371</v>
+        <v>20330051920184</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D69" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>20330051920171</v>
+        <v>20330051920154</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E70" t="s">
         <v>7</v>
@@ -5409,16 +5415,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>20330051920171</v>
+        <v>20330051920154</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -5429,56 +5435,56 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>20330051920171</v>
+        <v>20330051920186</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F72" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>20330051920171</v>
+        <v>20330051920186</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E73" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>20330051920172</v>
+        <v>20330051920388</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E74" t="s">
         <v>7</v>
@@ -5489,1422 +5495,22 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>20330051920172</v>
+        <v>20330051920388</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
       </c>
       <c r="F75" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920172</v>
-      </c>
-      <c r="B76" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76" t="s">
-        <v>73</v>
-      </c>
-      <c r="D76" t="s">
-        <v>146</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920172</v>
-      </c>
-      <c r="B77" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" t="s">
-        <v>73</v>
-      </c>
-      <c r="D77" t="s">
-        <v>146</v>
-      </c>
-      <c r="E77" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920173</v>
-      </c>
-      <c r="B78" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" t="s">
-        <v>147</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920173</v>
-      </c>
-      <c r="B79" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" t="s">
-        <v>147</v>
-      </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920173</v>
-      </c>
-      <c r="B80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C80" t="s">
-        <v>116</v>
-      </c>
-      <c r="D80" t="s">
-        <v>147</v>
-      </c>
-      <c r="E80" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920173</v>
-      </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" t="s">
-        <v>116</v>
-      </c>
-      <c r="D81" t="s">
-        <v>147</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920174</v>
-      </c>
-      <c r="B82" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" t="s">
-        <v>148</v>
-      </c>
-      <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920174</v>
-      </c>
-      <c r="B83" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="s">
-        <v>148</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920174</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" t="s">
-        <v>148</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920174</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="D85" t="s">
-        <v>148</v>
-      </c>
-      <c r="E85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920306</v>
-      </c>
-      <c r="B86" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" t="s">
-        <v>77</v>
-      </c>
-      <c r="D86" t="s">
-        <v>149</v>
-      </c>
-      <c r="E86" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920306</v>
-      </c>
-      <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>77</v>
-      </c>
-      <c r="D87" t="s">
-        <v>149</v>
-      </c>
-      <c r="E87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920306</v>
-      </c>
-      <c r="B88" t="s">
-        <v>87</v>
-      </c>
-      <c r="C88" t="s">
-        <v>77</v>
-      </c>
-      <c r="D88" t="s">
-        <v>149</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920306</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>77</v>
-      </c>
-      <c r="D89" t="s">
-        <v>149</v>
-      </c>
-      <c r="E89" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920177</v>
-      </c>
-      <c r="B90" t="s">
-        <v>88</v>
-      </c>
-      <c r="C90" t="s">
-        <v>117</v>
-      </c>
-      <c r="D90" t="s">
-        <v>150</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920177</v>
-      </c>
-      <c r="B91" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" t="s">
-        <v>150</v>
-      </c>
-      <c r="E91" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920177</v>
-      </c>
-      <c r="B92" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" t="s">
-        <v>150</v>
-      </c>
-      <c r="E92" t="s">
-        <v>6</v>
-      </c>
-      <c r="F92" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920177</v>
-      </c>
-      <c r="B93" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" t="s">
-        <v>150</v>
-      </c>
-      <c r="E93" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920178</v>
-      </c>
-      <c r="B94" t="s">
-        <v>89</v>
-      </c>
-      <c r="C94" t="s">
-        <v>118</v>
-      </c>
-      <c r="D94" t="s">
-        <v>151</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920178</v>
-      </c>
-      <c r="B95" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" t="s">
-        <v>118</v>
-      </c>
-      <c r="D95" t="s">
-        <v>151</v>
-      </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>20330051920178</v>
-      </c>
-      <c r="B96" t="s">
-        <v>89</v>
-      </c>
-      <c r="C96" t="s">
-        <v>118</v>
-      </c>
-      <c r="D96" t="s">
-        <v>151</v>
-      </c>
-      <c r="E96" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>20330051920178</v>
-      </c>
-      <c r="B97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C97" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" t="s">
-        <v>151</v>
-      </c>
-      <c r="E97" t="s">
-        <v>5</v>
-      </c>
-      <c r="F97" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>20330051920179</v>
-      </c>
-      <c r="B98" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" t="s">
-        <v>119</v>
-      </c>
-      <c r="D98" t="s">
-        <v>152</v>
-      </c>
-      <c r="E98" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>20330051920179</v>
-      </c>
-      <c r="B99" t="s">
-        <v>90</v>
-      </c>
-      <c r="C99" t="s">
-        <v>119</v>
-      </c>
-      <c r="D99" t="s">
-        <v>152</v>
-      </c>
-      <c r="E99" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>20330051920179</v>
-      </c>
-      <c r="B100" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" t="s">
-        <v>119</v>
-      </c>
-      <c r="D100" t="s">
-        <v>152</v>
-      </c>
-      <c r="E100" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>20330051920179</v>
-      </c>
-      <c r="B101" t="s">
-        <v>90</v>
-      </c>
-      <c r="C101" t="s">
-        <v>119</v>
-      </c>
-      <c r="D101" t="s">
-        <v>152</v>
-      </c>
-      <c r="E101" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>20330051920180</v>
-      </c>
-      <c r="B102" t="s">
-        <v>91</v>
-      </c>
-      <c r="C102" t="s">
-        <v>120</v>
-      </c>
-      <c r="D102" t="s">
-        <v>153</v>
-      </c>
-      <c r="E102" t="s">
-        <v>7</v>
-      </c>
-      <c r="F102" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>20330051920180</v>
-      </c>
-      <c r="B103" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" t="s">
-        <v>120</v>
-      </c>
-      <c r="D103" t="s">
-        <v>153</v>
-      </c>
-      <c r="E103" t="s">
-        <v>9</v>
-      </c>
-      <c r="F103" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>20330051920180</v>
-      </c>
-      <c r="B104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" t="s">
-        <v>120</v>
-      </c>
-      <c r="D104" t="s">
-        <v>153</v>
-      </c>
-      <c r="E104" t="s">
-        <v>6</v>
-      </c>
-      <c r="F104" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>20330051920180</v>
-      </c>
-      <c r="B105" t="s">
-        <v>91</v>
-      </c>
-      <c r="C105" t="s">
-        <v>120</v>
-      </c>
-      <c r="D105" t="s">
-        <v>153</v>
-      </c>
-      <c r="E105" t="s">
-        <v>5</v>
-      </c>
-      <c r="F105" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>20330051920373</v>
-      </c>
-      <c r="B106" t="s">
-        <v>92</v>
-      </c>
-      <c r="C106" t="s">
-        <v>70</v>
-      </c>
-      <c r="D106" t="s">
-        <v>154</v>
-      </c>
-      <c r="E106" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>20330051920373</v>
-      </c>
-      <c r="B107" t="s">
-        <v>92</v>
-      </c>
-      <c r="C107" t="s">
-        <v>70</v>
-      </c>
-      <c r="D107" t="s">
-        <v>154</v>
-      </c>
-      <c r="E107" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>20330051920373</v>
-      </c>
-      <c r="B108" t="s">
-        <v>92</v>
-      </c>
-      <c r="C108" t="s">
-        <v>70</v>
-      </c>
-      <c r="D108" t="s">
-        <v>154</v>
-      </c>
-      <c r="E108" t="s">
-        <v>6</v>
-      </c>
-      <c r="F108" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>20330051920373</v>
-      </c>
-      <c r="B109" t="s">
-        <v>92</v>
-      </c>
-      <c r="C109" t="s">
-        <v>70</v>
-      </c>
-      <c r="D109" t="s">
-        <v>154</v>
-      </c>
-      <c r="E109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>20330051920254</v>
-      </c>
-      <c r="B110" t="s">
-        <v>93</v>
-      </c>
-      <c r="C110" t="s">
-        <v>121</v>
-      </c>
-      <c r="D110" t="s">
-        <v>155</v>
-      </c>
-      <c r="E110" t="s">
-        <v>7</v>
-      </c>
-      <c r="F110" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>20330051920254</v>
-      </c>
-      <c r="B111" t="s">
-        <v>93</v>
-      </c>
-      <c r="C111" t="s">
-        <v>121</v>
-      </c>
-      <c r="D111" t="s">
-        <v>155</v>
-      </c>
-      <c r="E111" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>20330051920254</v>
-      </c>
-      <c r="B112" t="s">
-        <v>93</v>
-      </c>
-      <c r="C112" t="s">
-        <v>121</v>
-      </c>
-      <c r="D112" t="s">
-        <v>155</v>
-      </c>
-      <c r="E112" t="s">
-        <v>6</v>
-      </c>
-      <c r="F112" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>20330051920254</v>
-      </c>
-      <c r="B113" t="s">
-        <v>93</v>
-      </c>
-      <c r="C113" t="s">
-        <v>121</v>
-      </c>
-      <c r="D113" t="s">
-        <v>155</v>
-      </c>
-      <c r="E113" t="s">
-        <v>5</v>
-      </c>
-      <c r="F113" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>20330051920181</v>
-      </c>
-      <c r="B114" t="s">
-        <v>93</v>
-      </c>
-      <c r="C114" t="s">
-        <v>116</v>
-      </c>
-      <c r="D114" t="s">
-        <v>156</v>
-      </c>
-      <c r="E114" t="s">
-        <v>7</v>
-      </c>
-      <c r="F114" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>20330051920181</v>
-      </c>
-      <c r="B115" t="s">
-        <v>93</v>
-      </c>
-      <c r="C115" t="s">
-        <v>116</v>
-      </c>
-      <c r="D115" t="s">
-        <v>156</v>
-      </c>
-      <c r="E115" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>20330051920181</v>
-      </c>
-      <c r="B116" t="s">
-        <v>93</v>
-      </c>
-      <c r="C116" t="s">
-        <v>116</v>
-      </c>
-      <c r="D116" t="s">
-        <v>156</v>
-      </c>
-      <c r="E116" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>20330051920181</v>
-      </c>
-      <c r="B117" t="s">
-        <v>93</v>
-      </c>
-      <c r="C117" t="s">
-        <v>116</v>
-      </c>
-      <c r="D117" t="s">
-        <v>156</v>
-      </c>
-      <c r="E117" t="s">
-        <v>5</v>
-      </c>
-      <c r="F117" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>20330051920393</v>
-      </c>
-      <c r="B118" t="s">
-        <v>94</v>
-      </c>
-      <c r="C118" t="s">
-        <v>122</v>
-      </c>
-      <c r="D118" t="s">
-        <v>157</v>
-      </c>
-      <c r="E118" t="s">
-        <v>7</v>
-      </c>
-      <c r="F118" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>20330051920393</v>
-      </c>
-      <c r="B119" t="s">
-        <v>94</v>
-      </c>
-      <c r="C119" t="s">
-        <v>122</v>
-      </c>
-      <c r="D119" t="s">
-        <v>157</v>
-      </c>
-      <c r="E119" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>20330051920393</v>
-      </c>
-      <c r="B120" t="s">
-        <v>94</v>
-      </c>
-      <c r="C120" t="s">
-        <v>122</v>
-      </c>
-      <c r="D120" t="s">
-        <v>157</v>
-      </c>
-      <c r="E120" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>20330051920393</v>
-      </c>
-      <c r="B121" t="s">
-        <v>94</v>
-      </c>
-      <c r="C121" t="s">
-        <v>122</v>
-      </c>
-      <c r="D121" t="s">
-        <v>157</v>
-      </c>
-      <c r="E121" t="s">
-        <v>5</v>
-      </c>
-      <c r="F121" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>20330051920182</v>
-      </c>
-      <c r="B122" t="s">
-        <v>95</v>
-      </c>
-      <c r="C122" t="s">
-        <v>123</v>
-      </c>
-      <c r="D122" t="s">
-        <v>158</v>
-      </c>
-      <c r="E122" t="s">
-        <v>7</v>
-      </c>
-      <c r="F122" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>20330051920182</v>
-      </c>
-      <c r="B123" t="s">
-        <v>95</v>
-      </c>
-      <c r="C123" t="s">
-        <v>123</v>
-      </c>
-      <c r="D123" t="s">
-        <v>158</v>
-      </c>
-      <c r="E123" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>20330051920182</v>
-      </c>
-      <c r="B124" t="s">
-        <v>95</v>
-      </c>
-      <c r="C124" t="s">
-        <v>123</v>
-      </c>
-      <c r="D124" t="s">
-        <v>158</v>
-      </c>
-      <c r="E124" t="s">
-        <v>6</v>
-      </c>
-      <c r="F124" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>20330051920182</v>
-      </c>
-      <c r="B125" t="s">
-        <v>95</v>
-      </c>
-      <c r="C125" t="s">
-        <v>123</v>
-      </c>
-      <c r="D125" t="s">
-        <v>158</v>
-      </c>
-      <c r="E125" t="s">
-        <v>5</v>
-      </c>
-      <c r="F125" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>20330051920183</v>
-      </c>
-      <c r="B126" t="s">
-        <v>96</v>
-      </c>
-      <c r="C126" t="s">
-        <v>124</v>
-      </c>
-      <c r="D126" t="s">
-        <v>159</v>
-      </c>
-      <c r="E126" t="s">
-        <v>7</v>
-      </c>
-      <c r="F126" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>20330051920183</v>
-      </c>
-      <c r="B127" t="s">
-        <v>96</v>
-      </c>
-      <c r="C127" t="s">
-        <v>124</v>
-      </c>
-      <c r="D127" t="s">
-        <v>159</v>
-      </c>
-      <c r="E127" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>20330051920183</v>
-      </c>
-      <c r="B128" t="s">
-        <v>96</v>
-      </c>
-      <c r="C128" t="s">
-        <v>124</v>
-      </c>
-      <c r="D128" t="s">
-        <v>159</v>
-      </c>
-      <c r="E128" t="s">
-        <v>6</v>
-      </c>
-      <c r="F128" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>20330051920183</v>
-      </c>
-      <c r="B129" t="s">
-        <v>96</v>
-      </c>
-      <c r="C129" t="s">
-        <v>124</v>
-      </c>
-      <c r="D129" t="s">
-        <v>159</v>
-      </c>
-      <c r="E129" t="s">
-        <v>5</v>
-      </c>
-      <c r="F129" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>20330051920184</v>
-      </c>
-      <c r="B130" t="s">
-        <v>96</v>
-      </c>
-      <c r="C130" t="s">
-        <v>125</v>
-      </c>
-      <c r="D130" t="s">
-        <v>160</v>
-      </c>
-      <c r="E130" t="s">
-        <v>7</v>
-      </c>
-      <c r="F130" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>20330051920184</v>
-      </c>
-      <c r="B131" t="s">
-        <v>96</v>
-      </c>
-      <c r="C131" t="s">
-        <v>125</v>
-      </c>
-      <c r="D131" t="s">
-        <v>160</v>
-      </c>
-      <c r="E131" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>20330051920184</v>
-      </c>
-      <c r="B132" t="s">
-        <v>96</v>
-      </c>
-      <c r="C132" t="s">
-        <v>125</v>
-      </c>
-      <c r="D132" t="s">
-        <v>160</v>
-      </c>
-      <c r="E132" t="s">
-        <v>6</v>
-      </c>
-      <c r="F132" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>20330051920184</v>
-      </c>
-      <c r="B133" t="s">
-        <v>96</v>
-      </c>
-      <c r="C133" t="s">
-        <v>125</v>
-      </c>
-      <c r="D133" t="s">
-        <v>160</v>
-      </c>
-      <c r="E133" t="s">
-        <v>5</v>
-      </c>
-      <c r="F133" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>20330051920154</v>
-      </c>
-      <c r="B134" t="s">
-        <v>97</v>
-      </c>
-      <c r="C134" t="s">
-        <v>74</v>
-      </c>
-      <c r="D134" t="s">
-        <v>161</v>
-      </c>
-      <c r="E134" t="s">
-        <v>7</v>
-      </c>
-      <c r="F134" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>20330051920154</v>
-      </c>
-      <c r="B135" t="s">
-        <v>97</v>
-      </c>
-      <c r="C135" t="s">
-        <v>74</v>
-      </c>
-      <c r="D135" t="s">
-        <v>161</v>
-      </c>
-      <c r="E135" t="s">
-        <v>9</v>
-      </c>
-      <c r="F135" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>20330051920154</v>
-      </c>
-      <c r="B136" t="s">
-        <v>97</v>
-      </c>
-      <c r="C136" t="s">
-        <v>74</v>
-      </c>
-      <c r="D136" t="s">
-        <v>161</v>
-      </c>
-      <c r="E136" t="s">
-        <v>6</v>
-      </c>
-      <c r="F136" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>20330051920154</v>
-      </c>
-      <c r="B137" t="s">
-        <v>97</v>
-      </c>
-      <c r="C137" t="s">
-        <v>74</v>
-      </c>
-      <c r="D137" t="s">
-        <v>161</v>
-      </c>
-      <c r="E137" t="s">
-        <v>5</v>
-      </c>
-      <c r="F137" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>20330051920186</v>
-      </c>
-      <c r="B138" t="s">
-        <v>98</v>
-      </c>
-      <c r="C138" t="s">
-        <v>126</v>
-      </c>
-      <c r="D138" t="s">
-        <v>162</v>
-      </c>
-      <c r="E138" t="s">
-        <v>7</v>
-      </c>
-      <c r="F138" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>20330051920186</v>
-      </c>
-      <c r="B139" t="s">
-        <v>98</v>
-      </c>
-      <c r="C139" t="s">
-        <v>126</v>
-      </c>
-      <c r="D139" t="s">
-        <v>162</v>
-      </c>
-      <c r="E139" t="s">
-        <v>9</v>
-      </c>
-      <c r="F139" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>20330051920186</v>
-      </c>
-      <c r="B140" t="s">
-        <v>98</v>
-      </c>
-      <c r="C140" t="s">
-        <v>126</v>
-      </c>
-      <c r="D140" t="s">
-        <v>162</v>
-      </c>
-      <c r="E140" t="s">
-        <v>6</v>
-      </c>
-      <c r="F140" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>20330051920186</v>
-      </c>
-      <c r="B141" t="s">
-        <v>98</v>
-      </c>
-      <c r="C141" t="s">
-        <v>126</v>
-      </c>
-      <c r="D141" t="s">
-        <v>162</v>
-      </c>
-      <c r="E141" t="s">
-        <v>5</v>
-      </c>
-      <c r="F141" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>20330051920388</v>
-      </c>
-      <c r="B142" t="s">
-        <v>99</v>
-      </c>
-      <c r="C142" t="s">
-        <v>127</v>
-      </c>
-      <c r="D142" t="s">
-        <v>163</v>
-      </c>
-      <c r="E142" t="s">
-        <v>7</v>
-      </c>
-      <c r="F142" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>20330051920388</v>
-      </c>
-      <c r="B143" t="s">
-        <v>99</v>
-      </c>
-      <c r="C143" t="s">
-        <v>127</v>
-      </c>
-      <c r="D143" t="s">
-        <v>163</v>
-      </c>
-      <c r="E143" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>20330051920388</v>
-      </c>
-      <c r="B144" t="s">
-        <v>99</v>
-      </c>
-      <c r="C144" t="s">
-        <v>127</v>
-      </c>
-      <c r="D144" t="s">
-        <v>163</v>
-      </c>
-      <c r="E144" t="s">
-        <v>6</v>
-      </c>
-      <c r="F144" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>20330051920388</v>
-      </c>
-      <c r="B145" t="s">
-        <v>99</v>
-      </c>
-      <c r="C145" t="s">
-        <v>127</v>
-      </c>
-      <c r="D145" t="s">
-        <v>163</v>
-      </c>
-      <c r="E145" t="s">
-        <v>5</v>
-      </c>
-      <c r="F145" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6940,359 +5546,359 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920368</v>
+        <v>20330051920161</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920156</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920157</v>
+        <v>20330051920368</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920158</v>
+        <v>20330051920156</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920369</v>
+        <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920160</v>
+        <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920161</v>
+        <v>20330051920369</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920162</v>
+        <v>20330051920160</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920163</v>
+        <v>20330051920162</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920164</v>
+        <v>20330051920163</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920370</v>
+        <v>20330051920164</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920372</v>
+        <v>20330051920370</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920165</v>
+        <v>20330051920372</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920167</v>
+        <v>20330051920165</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920166</v>
+        <v>20330051920167</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920168</v>
+        <v>20330051920166</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920371</v>
+        <v>20330051920168</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920171</v>
+        <v>20330051920371</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920172</v>
+        <v>20330051920171</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920173</v>
+        <v>20330051920172</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920174</v>
+        <v>20330051920173</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7309,7 +5915,7 @@
         <v>149</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7326,7 +5932,7 @@
         <v>150</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7343,7 +5949,7 @@
         <v>151</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7360,7 +5966,7 @@
         <v>152</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7377,7 +5983,7 @@
         <v>153</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7394,7 +6000,7 @@
         <v>154</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7411,7 +6017,7 @@
         <v>155</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7428,7 +6034,7 @@
         <v>156</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7445,7 +6051,7 @@
         <v>157</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7462,7 +6068,7 @@
         <v>158</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7479,7 +6085,7 @@
         <v>159</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7496,7 +6102,7 @@
         <v>160</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7513,7 +6119,7 @@
         <v>161</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7530,7 +6136,7 @@
         <v>162</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7547,7 +6153,7 @@
         <v>163</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7557,7 +6163,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7587,6 +6193,1202 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920368</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920368</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920156</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920156</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920157</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920157</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920369</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920369</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920160</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920160</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920163</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920163</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920370</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920370</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920372</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920372</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920165</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920167</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920167</v>
+      </c>
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920166</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920166</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920168</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920168</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920371</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920371</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920171</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920171</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920172</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920306</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920306</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920179</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920180</v>
+      </c>
+      <c r="B36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920180</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920373</v>
+      </c>
+      <c r="B38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920373</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920254</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" t="s">
+        <v>156</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>20330051920181</v>
+      </c>
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>20330051920182</v>
+      </c>
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" t="s">
+        <v>158</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>20330051920182</v>
+      </c>
+      <c r="B45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920184</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>160</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>20330051920184</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" t="s">
+        <v>160</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>20330051920154</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>57</v>
+      </c>
+      <c r="G48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>20330051920154</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>58</v>
+      </c>
+      <c r="G49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>20330051920186</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>20330051920186</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" t="s">
+        <v>162</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G51">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>20330051920388</v>
+      </c>
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" t="s">
+        <v>163</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920388</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53" t="s">
+        <v>163</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -191,18 +191,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -221,15 +221,114 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ELELYN IVETH</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -239,21 +338,9 @@
     <t>BUSTOS</t>
   </si>
   <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>DEMUNER</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GASCA</t>
   </si>
   <si>
@@ -272,24 +359,9 @@
     <t>LOBATO</t>
   </si>
   <si>
-    <t>MATA</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -305,27 +377,15 @@
     <t>SANDRIA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>VELAZQEZ</t>
   </si>
   <si>
     <t>XOCUA</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -335,15 +395,6 @@
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -371,12 +422,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -389,30 +434,18 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
     <t>VICTORIANO</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>PATRICIA</t>
   </si>
   <si>
     <t>LUIS YAEL</t>
   </si>
   <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
     <t>DINA BERENICE</t>
   </si>
   <si>
@@ -422,18 +455,9 @@
     <t>SARAHI</t>
   </si>
   <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
     <t>ADRIANA ARELY</t>
   </si>
   <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
     <t>ARANTXA</t>
   </si>
   <si>
@@ -458,24 +482,9 @@
     <t>DANIELA RUBI</t>
   </si>
   <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
     <t>VANNIA GISELLE</t>
   </si>
   <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
     <t>ESTHER ARISBETH</t>
   </si>
   <si>
@@ -494,12 +503,6 @@
     <t>MONSERRATH YARETZY</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ELELYN IVETH</t>
-  </si>
-  <si>
     <t>MARIAN</t>
   </si>
   <si>
@@ -507,9 +510,6 @@
   </si>
   <si>
     <t>AYARI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
   </si>
 </sst>
 </file>
@@ -1001,13 +1001,13 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1055,13 +1055,13 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -1078,13 +1078,13 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1132,13 +1132,13 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1155,7 +1155,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1209,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1232,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1286,13 +1286,13 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1309,13 +1309,13 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1363,13 +1363,13 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1386,13 +1386,13 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -1440,13 +1440,13 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1463,13 +1463,13 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>8</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>7</v>
@@ -1517,13 +1517,13 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1617,13 +1617,13 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1671,13 +1671,13 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1771,13 +1771,13 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>9</v>
@@ -1825,13 +1825,13 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1848,13 +1848,13 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>8</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -1902,13 +1902,13 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1925,13 +1925,13 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>10</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -1979,13 +1979,13 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -2002,13 +2002,13 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -2056,13 +2056,13 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2079,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>8</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -2133,13 +2133,13 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2156,13 +2156,13 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>7</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -2210,13 +2210,13 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2233,13 +2233,13 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2287,13 +2287,13 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2310,13 +2310,13 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -2364,13 +2364,13 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -2441,7 +2441,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2464,13 +2464,13 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2518,13 +2518,13 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2618,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2672,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2695,7 +2695,7 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -2749,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2772,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -2826,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2849,13 +2849,13 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>9</v>
@@ -2903,13 +2903,13 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2926,13 +2926,13 @@
         <v>6</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -2980,13 +2980,13 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -3003,13 +3003,13 @@
         <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E30">
         <v>9</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G30">
         <v>7</v>
@@ -3057,13 +3057,13 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3080,13 +3080,13 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>9</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>10</v>
@@ -3134,13 +3134,13 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3157,13 +3157,13 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3211,13 +3211,13 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3234,13 +3234,13 @@
         <v>6</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E33">
         <v>7</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3288,13 +3288,13 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>7</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3311,7 +3311,7 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3365,7 +3365,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3388,7 +3388,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3442,7 +3442,7 @@
         <v>5</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3465,13 +3465,13 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E36">
         <v>9</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>8</v>
@@ -3519,13 +3519,13 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3542,13 +3542,13 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E37">
         <v>9</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -3596,13 +3596,13 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3619,13 +3619,13 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>9</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>8</v>
@@ -3673,13 +3673,13 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3696,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3824,27 +3824,30 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.8</v>
+      </c>
       <c r="I2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -3853,27 +3856,30 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>27</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>75</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>36</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3882,19 +3888,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>86.11</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>13.89</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3905,7 +3911,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3914,25 +3920,25 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>86.11</v>
+        <v>94.44</v>
       </c>
       <c r="G5">
-        <v>13.89</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4006,7 +4012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4035,19 +4041,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -4055,79 +4061,79 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920368</v>
+        <v>20330051920161</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920156</v>
+        <v>20330051920162</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920156</v>
+        <v>20330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920164</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
@@ -4135,119 +4141,119 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920174</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920174</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920369</v>
+        <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920369</v>
+        <v>20330051920306</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920160</v>
+        <v>20330051920177</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -4255,39 +4261,39 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920160</v>
+        <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920161</v>
+        <v>20330051920182</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
@@ -4295,1222 +4301,42 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920161</v>
+        <v>20330051920183</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920161</v>
+        <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920162</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920162</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920163</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920163</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920164</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920164</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920370</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920370</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920372</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920372</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920165</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920165</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920167</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920167</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920166</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920166</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920168</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920168</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920371</v>
-      </c>
-      <c r="B35" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920371</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920171</v>
-      </c>
-      <c r="B37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>145</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920171</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920172</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920172</v>
-      </c>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920173</v>
-      </c>
-      <c r="B41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>147</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920173</v>
-      </c>
-      <c r="B42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" t="s">
-        <v>147</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920174</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D43" t="s">
-        <v>148</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920174</v>
-      </c>
-      <c r="B44" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920174</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920306</v>
-      </c>
-      <c r="B46" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" t="s">
-        <v>149</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920306</v>
-      </c>
-      <c r="B47" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" t="s">
-        <v>77</v>
-      </c>
-      <c r="D47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920177</v>
-      </c>
-      <c r="B48" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920177</v>
-      </c>
-      <c r="B49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" t="s">
-        <v>117</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920178</v>
-      </c>
-      <c r="B50" t="s">
-        <v>89</v>
-      </c>
-      <c r="C50" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" t="s">
-        <v>151</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920178</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920179</v>
-      </c>
-      <c r="B52" t="s">
-        <v>90</v>
-      </c>
-      <c r="C52" t="s">
-        <v>119</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920179</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" t="s">
-        <v>119</v>
-      </c>
-      <c r="D53" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920180</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" t="s">
-        <v>120</v>
-      </c>
-      <c r="D54" t="s">
-        <v>153</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920180</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" t="s">
-        <v>120</v>
-      </c>
-      <c r="D55" t="s">
-        <v>153</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920373</v>
-      </c>
-      <c r="B56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" t="s">
-        <v>154</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920373</v>
-      </c>
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920254</v>
-      </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" t="s">
-        <v>121</v>
-      </c>
-      <c r="D58" t="s">
-        <v>155</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920254</v>
-      </c>
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" t="s">
-        <v>155</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920181</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" t="s">
-        <v>156</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920181</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
-      </c>
-      <c r="C61" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" t="s">
-        <v>156</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920393</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" t="s">
-        <v>157</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920393</v>
-      </c>
-      <c r="B63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" t="s">
-        <v>122</v>
-      </c>
-      <c r="D63" t="s">
-        <v>157</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920182</v>
-      </c>
-      <c r="B64" t="s">
-        <v>95</v>
-      </c>
-      <c r="C64" t="s">
-        <v>123</v>
-      </c>
-      <c r="D64" t="s">
-        <v>158</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920182</v>
-      </c>
-      <c r="B65" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920183</v>
-      </c>
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920183</v>
-      </c>
-      <c r="B67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" t="s">
-        <v>124</v>
-      </c>
-      <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920184</v>
-      </c>
-      <c r="B68" t="s">
-        <v>96</v>
-      </c>
-      <c r="C68" t="s">
-        <v>125</v>
-      </c>
-      <c r="D68" t="s">
-        <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920184</v>
-      </c>
-      <c r="B69" t="s">
-        <v>96</v>
-      </c>
-      <c r="C69" t="s">
-        <v>125</v>
-      </c>
-      <c r="D69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920154</v>
-      </c>
-      <c r="B70" t="s">
-        <v>97</v>
-      </c>
-      <c r="C70" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" t="s">
-        <v>161</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920154</v>
-      </c>
-      <c r="B71" t="s">
-        <v>97</v>
-      </c>
-      <c r="C71" t="s">
-        <v>74</v>
-      </c>
-      <c r="D71" t="s">
-        <v>161</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920186</v>
-      </c>
-      <c r="B72" t="s">
-        <v>98</v>
-      </c>
-      <c r="C72" t="s">
-        <v>126</v>
-      </c>
-      <c r="D72" t="s">
-        <v>162</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920186</v>
-      </c>
-      <c r="B73" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" t="s">
-        <v>126</v>
-      </c>
-      <c r="D73" t="s">
-        <v>162</v>
-      </c>
-      <c r="E73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920388</v>
-      </c>
-      <c r="B74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" t="s">
-        <v>127</v>
-      </c>
-      <c r="D74" t="s">
-        <v>163</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920388</v>
-      </c>
-      <c r="B75" t="s">
-        <v>99</v>
-      </c>
-      <c r="C75" t="s">
-        <v>127</v>
-      </c>
-      <c r="D75" t="s">
-        <v>163</v>
-      </c>
-      <c r="E75" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5546,16 +4372,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920161</v>
+        <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5563,41 +4389,41 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920174</v>
+        <v>20330051920162</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920156</v>
+        <v>20330051920161</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -5606,554 +4432,554 @@
         <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920164</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920158</v>
+        <v>20330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920369</v>
+        <v>20330051920306</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920160</v>
+        <v>20330051920177</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920162</v>
+        <v>20330051920178</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920163</v>
+        <v>20330051920182</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920164</v>
+        <v>20330051920183</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920370</v>
+        <v>20330051920388</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920372</v>
+        <v>20330051920368</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920165</v>
+        <v>20330051920156</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920167</v>
+        <v>20330051920158</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920166</v>
+        <v>20330051920369</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920168</v>
+        <v>20330051920160</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920371</v>
+        <v>20330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920171</v>
+        <v>20330051920370</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920172</v>
+        <v>20330051920372</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920173</v>
+        <v>20330051920165</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920306</v>
+        <v>20330051920167</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920177</v>
+        <v>20330051920166</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920178</v>
+        <v>20330051920168</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920179</v>
+        <v>20330051920371</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920180</v>
+        <v>20330051920171</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920373</v>
+        <v>20330051920173</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920254</v>
+        <v>20330051920179</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920181</v>
+        <v>20330051920180</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920393</v>
+        <v>20330051920373</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920182</v>
+        <v>20330051920254</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920183</v>
+        <v>20330051920181</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920184</v>
+        <v>20330051920393</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920154</v>
+        <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920186</v>
+        <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920388</v>
+        <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6163,7 +4989,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6195,19 +5021,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920368</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -6218,30 +5044,30 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920368</v>
+        <v>20330051920158</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920156</v>
+        <v>20330051920161</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6250,13 +5076,13 @@
         <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6264,22 +5090,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920156</v>
+        <v>20330051920172</v>
       </c>
       <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
         <v>68</v>
       </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6287,45 +5113,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920306</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6333,45 +5159,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920369</v>
+        <v>20330051920393</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920369</v>
+        <v>20330051920182</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6379,1013 +5205,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920160</v>
+        <v>20330051920388</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920160</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920163</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920163</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920370</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920370</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920372</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920372</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920165</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920165</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920167</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920167</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920166</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920166</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920168</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920168</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920371</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920371</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920171</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920171</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>115</v>
-      </c>
-      <c r="D29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920172</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920172</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920306</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920306</v>
-      </c>
-      <c r="B33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" t="s">
-        <v>149</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920179</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" t="s">
-        <v>152</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920179</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920180</v>
-      </c>
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920180</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920373</v>
-      </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" t="s">
-        <v>154</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920373</v>
-      </c>
-      <c r="B39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920254</v>
-      </c>
-      <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D40" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920254</v>
-      </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>20330051920181</v>
-      </c>
-      <c r="B42" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" t="s">
-        <v>156</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>20330051920181</v>
-      </c>
-      <c r="B43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" t="s">
-        <v>116</v>
-      </c>
-      <c r="D43" t="s">
-        <v>156</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>20330051920182</v>
-      </c>
-      <c r="B44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D44" t="s">
-        <v>158</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>20330051920182</v>
-      </c>
-      <c r="B45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" t="s">
-        <v>123</v>
-      </c>
-      <c r="D45" t="s">
-        <v>158</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>20330051920184</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>20330051920184</v>
-      </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" t="s">
-        <v>160</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>20330051920154</v>
-      </c>
-      <c r="B48" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" t="s">
-        <v>74</v>
-      </c>
-      <c r="D48" t="s">
-        <v>161</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>20330051920154</v>
-      </c>
-      <c r="B49" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>74</v>
-      </c>
-      <c r="D49" t="s">
-        <v>161</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>20330051920186</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" t="s">
-        <v>126</v>
-      </c>
-      <c r="D50" t="s">
-        <v>162</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>57</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>20330051920186</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>58</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>20330051920388</v>
-      </c>
-      <c r="B52" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" t="s">
-        <v>163</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>57</v>
-      </c>
-      <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>20330051920388</v>
-      </c>
-      <c r="B53" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" t="s">
-        <v>163</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>58</v>
-      </c>
-      <c r="G53">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -149,7 +149,7 @@
     <t>TORRES MELO DIEGO</t>
   </si>
   <si>
-    <t>VAZQUEZ TEPEPA ELELYN IVETH</t>
+    <t>VAZQUEZ TEPEPA EVELYN IVETH</t>
   </si>
   <si>
     <t>VAZQUEZ VICTORIANO MARIAN</t>
@@ -200,15 +200,15 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,235 +224,235 @@
     <t>ARROYO</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>CANSECO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>EVELYN IVETH</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
   </si>
   <si>
     <t>LEAL</t>
   </si>
   <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
   </si>
   <si>
     <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ELELYN IVETH</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VELAZQEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
   </si>
   <si>
     <t>ADRIANA ARELY</t>
@@ -1022,13 +1022,13 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1058,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1099,13 +1099,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1135,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1176,13 +1176,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1212,13 +1212,13 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1253,13 +1253,13 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1330,13 +1330,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1407,13 +1407,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1457,7 +1457,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -1484,13 +1484,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1511,7 +1511,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1540,7 +1540,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1561,13 +1561,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1594,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1638,13 +1638,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1715,13 +1715,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1751,7 +1751,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -1792,13 +1792,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1869,13 +1869,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1905,7 +1905,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1946,13 +1946,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2023,13 +2023,13 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2059,7 +2059,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2100,13 +2100,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2136,7 +2136,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2177,13 +2177,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2213,7 +2213,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2254,13 +2254,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2331,13 +2331,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2367,7 +2367,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2408,13 +2408,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2444,13 +2444,13 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2485,13 +2485,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2521,7 +2521,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2535,13 +2535,13 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2562,13 +2562,13 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2589,16 +2589,16 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -2639,13 +2639,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2675,7 +2675,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>-1</v>
@@ -2716,13 +2716,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2752,7 +2752,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>-1</v>
@@ -2793,13 +2793,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2829,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>-1</v>
@@ -2870,13 +2870,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2906,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2947,13 +2947,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2983,7 +2983,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3024,13 +3024,13 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3101,13 +3101,13 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3137,7 +3137,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3178,13 +3178,13 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3214,13 +3214,13 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3255,13 +3255,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3291,7 +3291,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3332,13 +3332,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3368,7 +3368,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>-1</v>
@@ -3409,13 +3409,13 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3445,7 +3445,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>-1</v>
@@ -3486,13 +3486,13 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3563,13 +3563,13 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3605,7 +3605,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3640,13 +3640,13 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3717,13 +3717,13 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3759,7 +3759,7 @@
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3856,19 +3856,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>30.56</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3923,27 +3923,27 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>94.44</v>
       </c>
       <c r="G5">
+        <v>5.56</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>8.9</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
       <c r="J5">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3952,30 +3952,30 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -3984,19 +3984,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4012,7 +4012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4047,10 +4047,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4061,50 +4061,50 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920161</v>
+        <v>20330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920162</v>
+        <v>20330051920164</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920162</v>
+        <v>20330051920172</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
@@ -4121,13 +4121,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920164</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
@@ -4141,13 +4141,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920172</v>
+        <v>20330051920306</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
@@ -4161,36 +4161,36 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920174</v>
+        <v>20330051920177</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4201,36 +4201,36 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920306</v>
+        <v>20330051920183</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -4241,101 +4241,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920177</v>
+        <v>20330051920388</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920178</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920182</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920183</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920388</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4372,19 +4292,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920174</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4392,30 +4312,30 @@
         <v>20330051920162</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920157</v>
+        <v>20330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4423,16 +4343,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920161</v>
+        <v>20330051920172</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4440,13 +4360,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920164</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
@@ -4457,13 +4377,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920172</v>
+        <v>20330051920306</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
@@ -4474,7 +4394,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920306</v>
+        <v>20330051920177</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
@@ -4483,7 +4403,7 @@
         <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4491,7 +4411,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920177</v>
+        <v>20330051920178</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
@@ -4500,7 +4420,7 @@
         <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4508,7 +4428,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920178</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
@@ -4517,7 +4437,7 @@
         <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4525,7 +4445,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920183</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
@@ -4534,7 +4454,7 @@
         <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4542,7 +4462,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920183</v>
+        <v>20330051920388</v>
       </c>
       <c r="B12" t="s">
         <v>77</v>
@@ -4551,7 +4471,7 @@
         <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4559,30 +4479,30 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920388</v>
+        <v>20330051920368</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920368</v>
+        <v>20330051920156</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
@@ -4593,13 +4513,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920156</v>
+        <v>20330051920158</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
@@ -4610,13 +4530,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920158</v>
+        <v>20330051920369</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
@@ -4627,13 +4547,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920369</v>
+        <v>20330051920160</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
@@ -4644,13 +4564,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920160</v>
+        <v>20330051920161</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
@@ -4664,10 +4584,10 @@
         <v>20330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4681,10 +4601,10 @@
         <v>20330051920370</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4698,10 +4618,10 @@
         <v>20330051920372</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4715,10 +4635,10 @@
         <v>20330051920165</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4732,10 +4652,10 @@
         <v>20330051920167</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4749,10 +4669,10 @@
         <v>20330051920166</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4766,10 +4686,10 @@
         <v>20330051920168</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4783,10 +4703,10 @@
         <v>20330051920371</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4800,10 +4720,10 @@
         <v>20330051920171</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -4817,10 +4737,10 @@
         <v>20330051920173</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4834,10 +4754,10 @@
         <v>20330051920179</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4851,10 +4771,10 @@
         <v>20330051920180</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4868,10 +4788,10 @@
         <v>20330051920373</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4885,10 +4805,10 @@
         <v>20330051920254</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4902,10 +4822,10 @@
         <v>20330051920181</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4919,10 +4839,10 @@
         <v>20330051920393</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4936,10 +4856,10 @@
         <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -4953,10 +4873,10 @@
         <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -4970,10 +4890,10 @@
         <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -4989,7 +4909,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5027,10 +4947,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -5044,16 +4964,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920158</v>
+        <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5067,22 +4987,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920161</v>
+        <v>20330051920388</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5090,39 +5010,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920172</v>
+        <v>20330051920388</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920173</v>
+        <v>20330051920158</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5136,16 +5056,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920306</v>
+        <v>20330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5159,16 +5079,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920393</v>
+        <v>20330051920173</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5182,16 +5102,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920182</v>
+        <v>20330051920306</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5205,24 +5125,47 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920388</v>
+        <v>20330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920182</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
         <v>57</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -191,24 +191,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,18 +221,63 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
     <t>MATA</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>NAMORADO</t>
   </si>
   <si>
@@ -245,28 +290,85 @@
     <t>QUIRIZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
     <t>TINOCO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MACARIO</t>
@@ -275,27 +377,93 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>MELO</t>
   </si>
   <si>
     <t>TEPEPA</t>
   </si>
   <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
     <t>ANGELES NAHOMI</t>
   </si>
   <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
     <t>AISHA NAOMI</t>
   </si>
   <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
     <t>CRISTIAN ARTURO</t>
   </si>
   <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
@@ -308,208 +476,40 @@
     <t>MONICA</t>
   </si>
   <si>
+    <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
     <t>EVELYN IVETH</t>
   </si>
   <si>
+    <t>MARIAN</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>AYARI</t>
+  </si>
+  <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VELAZQEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>MARIAN</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>AYARI</t>
   </si>
 </sst>
 </file>
@@ -1013,19 +1013,19 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1090,19 +1090,19 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1126,19 +1126,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>6</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1161,25 +1161,25 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1206,16 +1206,16 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1244,19 +1244,19 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1283,7 +1283,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1321,19 +1321,19 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1398,19 +1398,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1440,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1475,19 +1475,19 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>6</v>
@@ -1511,7 +1511,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1523,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1546,25 +1546,25 @@
         <v>5</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1591,16 +1591,16 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1629,19 +1629,19 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1668,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1700,16 +1700,16 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1718,7 +1718,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1742,7 +1742,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1754,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1783,19 +1783,19 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>9</v>
@@ -1822,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1831,7 +1831,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1860,19 +1860,19 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1896,13 +1896,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>6</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1937,19 +1937,19 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1976,7 +1976,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -2014,19 +2014,19 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -2050,19 +2050,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2091,19 +2091,19 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2127,10 +2127,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2168,19 +2168,19 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2210,13 +2210,13 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2245,19 +2245,19 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2284,7 +2284,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2322,19 +2322,19 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2361,16 +2361,16 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2393,25 +2393,25 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2435,19 +2435,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2476,19 +2476,19 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2512,7 +2512,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2524,7 +2524,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2547,25 +2547,25 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2601,7 +2601,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2624,25 +2624,25 @@
         <v>6</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>5</v>
@@ -2666,19 +2666,19 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>5</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>8</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2701,25 +2701,25 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2746,16 +2746,16 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2778,16 +2778,16 @@
         <v>8</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2796,7 +2796,7 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2832,7 +2832,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2861,19 +2861,19 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2903,13 +2903,13 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2938,19 +2938,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2974,13 +2974,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3015,19 +3015,19 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -3054,16 +3054,16 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3092,19 +3092,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3128,13 +3128,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>6</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3169,19 +3169,19 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -3246,19 +3246,19 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -3285,16 +3285,16 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3317,25 +3317,25 @@
         <v>6</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>8</v>
@@ -3365,13 +3365,13 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3394,25 +3394,25 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3448,7 +3448,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3477,19 +3477,19 @@
         <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
         <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3519,13 +3519,13 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3554,19 +3554,19 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -3590,13 +3590,13 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3631,19 +3631,19 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>8</v>
@@ -3667,7 +3667,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>6</v>
@@ -3702,25 +3702,25 @@
         <v>7</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G39">
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -3747,16 +3747,16 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>7</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -3824,25 +3824,25 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>69.44</v>
+        <v>58.33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>41.67</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3879,7 +3879,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3888,19 +3888,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>86.11</v>
+        <v>77.78</v>
       </c>
       <c r="G4">
-        <v>13.89</v>
+        <v>22.22</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3952,19 +3952,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>97.22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4012,7 +4012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4037,226 +4037,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920157</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920172</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920174</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920306</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920177</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920178</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920182</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920183</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920388</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4292,200 +4072,200 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920162</v>
+        <v>20330051920156</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920164</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920172</v>
+        <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920174</v>
+        <v>20330051920369</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920306</v>
+        <v>20330051920160</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920177</v>
+        <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920178</v>
+        <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920182</v>
+        <v>20330051920163</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920183</v>
+        <v>20330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920388</v>
+        <v>20330051920370</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920368</v>
+        <v>20330051920372</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -4496,13 +4276,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920156</v>
+        <v>20330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
@@ -4513,13 +4293,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920158</v>
+        <v>20330051920167</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
@@ -4530,13 +4310,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920369</v>
+        <v>20330051920166</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
@@ -4547,13 +4327,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920160</v>
+        <v>20330051920168</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
@@ -4564,13 +4344,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920161</v>
+        <v>20330051920371</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
@@ -4581,13 +4361,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920163</v>
+        <v>20330051920171</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4598,13 +4378,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920370</v>
+        <v>20330051920172</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4615,13 +4395,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920372</v>
+        <v>20330051920173</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4632,13 +4412,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920165</v>
+        <v>20330051920174</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4649,13 +4429,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920167</v>
+        <v>20330051920306</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4666,13 +4446,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920166</v>
+        <v>20330051920177</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4683,13 +4463,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920168</v>
+        <v>20330051920178</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4700,13 +4480,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920371</v>
+        <v>20330051920179</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4717,13 +4497,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920171</v>
+        <v>20330051920180</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -4734,13 +4514,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920173</v>
+        <v>20330051920373</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4751,13 +4531,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920179</v>
+        <v>20330051920254</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4768,13 +4548,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920180</v>
+        <v>20330051920181</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4785,13 +4565,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920373</v>
+        <v>20330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4802,13 +4582,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920254</v>
+        <v>20330051920182</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4819,13 +4599,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920181</v>
+        <v>20330051920183</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4836,13 +4616,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920393</v>
+        <v>20330051920184</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4853,13 +4633,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920184</v>
+        <v>20330051920154</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -4870,13 +4650,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920154</v>
+        <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -4887,13 +4667,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920186</v>
+        <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -4909,7 +4689,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4941,39 +4721,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920173</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920157</v>
+        <v>20330051920173</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4987,39 +4767,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920388</v>
+        <v>20330051920393</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920388</v>
+        <v>20330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5033,22 +4813,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920158</v>
+        <v>20330051920183</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5056,39 +4836,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920172</v>
+        <v>20330051920183</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920173</v>
+        <v>20330051920158</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5102,45 +4882,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920306</v>
+        <v>20330051920369</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920393</v>
+        <v>20330051920167</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5148,25 +4928,94 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920172</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920180</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920373</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920154</v>
+      </c>
+      <c r="B14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -200,10 +200,10 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Vargas Olvera Francisco Eduardo</t>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1040,13 +1040,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1058,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1108,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1117,16 +1117,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1141,7 +1141,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1185,7 +1185,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1194,13 +1194,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1215,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1262,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1271,13 +1271,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1339,7 +1339,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1348,13 +1348,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1416,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1425,13 +1425,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1493,7 +1493,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1502,16 +1502,16 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1523,10 +1523,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1570,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1579,16 +1579,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1597,13 +1597,13 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1647,7 +1647,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1656,13 +1656,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1724,7 +1724,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1733,13 +1733,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1801,7 +1801,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1810,13 +1810,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1831,10 +1831,10 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1878,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1887,13 +1887,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1964,13 +1964,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -2032,7 +2032,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2041,13 +2041,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2065,7 +2065,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2109,7 +2109,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2118,16 +2118,16 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2142,7 +2142,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2186,7 +2186,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2195,13 +2195,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2219,7 +2219,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2263,7 +2263,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2272,13 +2272,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2340,7 +2340,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2349,13 +2349,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2426,16 +2426,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2494,7 +2494,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2503,13 +2503,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2571,7 +2571,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2580,16 +2580,16 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2601,7 +2601,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2648,7 +2648,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2657,16 +2657,16 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -2678,10 +2678,10 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2725,7 +2725,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2734,13 +2734,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2755,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2802,7 +2802,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2811,13 +2811,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2879,7 +2879,7 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2888,16 +2888,16 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -2912,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2956,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2965,13 +2965,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2989,7 +2989,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3033,7 +3033,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3042,13 +3042,13 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3063,7 +3063,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3110,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3119,13 +3119,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3143,7 +3143,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3187,7 +3187,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3196,16 +3196,16 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3217,10 +3217,10 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3264,7 +3264,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3273,13 +3273,13 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3294,10 +3294,10 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3341,7 +3341,7 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3350,13 +3350,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3371,10 +3371,10 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3418,7 +3418,7 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3427,16 +3427,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>5</v>
@@ -3451,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3495,7 +3495,7 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3504,13 +3504,13 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3572,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3581,13 +3581,13 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3602,10 +3602,10 @@
         <v>9</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3649,7 +3649,7 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3658,13 +3658,13 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3679,10 +3679,10 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3726,7 +3726,7 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3735,13 +3735,13 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
         <v>7</v>
@@ -3753,10 +3753,10 @@
         <v>8</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3856,19 +3856,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="G3">
-        <v>30.56</v>
+        <v>16.67</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3888,19 +3888,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="G4">
-        <v>22.22</v>
+        <v>8.33</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3920,19 +3920,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="G5">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3964,7 +3964,7 @@
         <v>2.78</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4689,7 +4689,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4721,22 +4721,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920173</v>
+        <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4744,16 +4744,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920173</v>
+        <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4767,22 +4767,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920393</v>
+        <v>20330051920173</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4790,16 +4790,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920393</v>
+        <v>20330051920173</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4813,16 +4813,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920183</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4836,16 +4836,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920183</v>
+        <v>20330051920174</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920388</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4882,22 +4882,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920369</v>
+        <v>20330051920388</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4905,16 +4905,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920167</v>
+        <v>20330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4928,16 +4928,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920172</v>
+        <v>20330051920162</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4951,16 +4951,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920180</v>
+        <v>20330051920167</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4974,16 +4974,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920373</v>
+        <v>20330051920172</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -4997,16 +4997,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920154</v>
+        <v>20330051920177</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5015,6 +5015,121 @@
         <v>57</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920180</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920373</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920393</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920183</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920154</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -1034,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1111,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1188,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1283,7 +1283,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1342,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1496,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1573,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1591,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1727,7 +1727,7 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1804,7 +1804,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1822,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1958,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1976,7 +1976,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -2035,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2053,7 +2053,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2112,7 +2112,7 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2130,7 +2130,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2266,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2343,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2420,7 +2420,7 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2497,7 +2497,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2515,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2574,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2651,7 +2651,7 @@
         <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2669,7 +2669,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2805,7 +2805,7 @@
         <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2882,7 +2882,7 @@
         <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2959,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3036,7 +3036,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3054,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3113,7 +3113,7 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3190,7 +3190,7 @@
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3267,7 +3267,7 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3344,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3421,7 +3421,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3439,7 +3439,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3498,7 +3498,7 @@
         <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3575,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3652,7 +3652,7 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3729,7 +3729,7 @@
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3824,16 +3824,16 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>58.33</v>
+        <v>72.22</v>
       </c>
       <c r="G2">
-        <v>41.67</v>
+        <v>27.78</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -4689,7 +4689,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4767,22 +4767,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4790,16 +4790,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4813,16 +4813,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920174</v>
+        <v>20330051920388</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4836,16 +4836,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920174</v>
+        <v>20330051920388</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4859,16 +4859,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920388</v>
+        <v>20330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4882,22 +4882,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920388</v>
+        <v>20330051920373</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4905,16 +4905,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920369</v>
+        <v>20330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4928,16 +4928,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920162</v>
+        <v>20330051920154</v>
       </c>
       <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" t="s">
         <v>74</v>
       </c>
-      <c r="C11" t="s">
-        <v>106</v>
-      </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4946,190 +4946,6 @@
         <v>57</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920167</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920172</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920177</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920180</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920373</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920393</v>
-      </c>
-      <c r="B17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" t="s">
-        <v>157</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920183</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920154</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>161</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20212.xlsx
+++ b/grupos/4ARHM - Estadisticos 20212.xlsx
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -1114,7 +1114,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1191,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1268,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1345,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1422,7 +1422,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1499,7 +1499,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1594,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -1730,7 +1730,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -1807,7 +1807,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1884,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1961,7 +1961,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -2038,7 +2038,7 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2115,7 +2115,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2192,7 +2192,7 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2210,7 +2210,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2269,7 +2269,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2346,7 +2346,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>6</v>
@@ -2577,7 +2577,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>6</v>
@@ -2654,7 +2654,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2672,7 +2672,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2731,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -2808,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>6</v>
@@ -2826,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2885,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>9</v>
@@ -2903,7 +2903,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2962,7 +2962,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3039,7 +3039,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3116,7 +3116,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3193,7 +3193,7 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -3347,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>9</v>
@@ -3365,7 +3365,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3424,7 +3424,7 @@
         <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3501,7 +3501,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3578,7 +3578,7 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3655,7 +3655,7 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -3732,7 +3732,7 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>6</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
